--- a/AAII_Financials/Quarterly/HUTCY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/HUTCY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="448" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="492" uniqueCount="92">
   <si>
     <t>HUTCY</t>
   </si>
@@ -656,91 +656,99 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:S102"/>
+  <dimension ref="A5:U102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44196</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>44012</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>43830</v>
       </c>
     </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -783,17 +791,23 @@
       <c r="P8" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="Q8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S8" s="3">
         <v>328200</v>
       </c>
-      <c r="R8" s="3">
+      <c r="T8" s="3">
         <v>253400</v>
       </c>
-      <c r="S8" s="3">
+      <c r="U8" s="3">
         <v>393200</v>
       </c>
     </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -836,17 +850,23 @@
       <c r="P9" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="Q9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S9" s="3">
         <v>118200</v>
       </c>
-      <c r="R9" s="3">
+      <c r="T9" s="3">
         <v>40300</v>
       </c>
-      <c r="S9" s="3">
+      <c r="U9" s="3">
         <v>156000</v>
       </c>
     </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
@@ -889,17 +909,23 @@
       <c r="P10" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="Q10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S10" s="3">
         <v>210000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="T10" s="3">
         <v>213100</v>
       </c>
-      <c r="S10" s="3">
+      <c r="U10" s="3">
         <v>237200</v>
       </c>
     </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -919,8 +945,10 @@
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
       <c r="S11" s="3"/>
-    </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T11" s="3"/>
+      <c r="U11" s="3"/>
+    </row>
+    <row r="12" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -972,8 +1000,14 @@
       <c r="S12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="U12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1025,8 +1059,14 @@
       <c r="S13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T13" s="3">
+        <v>0</v>
+      </c>
+      <c r="U13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1078,8 +1118,14 @@
       <c r="S14" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="U14" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="15" spans="1:21" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1122,17 +1168,23 @@
       <c r="P15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="Q15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S15" s="3">
         <v>78900</v>
       </c>
-      <c r="R15" s="3">
+      <c r="T15" s="3">
         <v>77700</v>
       </c>
-      <c r="S15" s="3">
+      <c r="U15" s="3">
         <v>77400</v>
       </c>
     </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:21" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1149,8 +1201,10 @@
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
       <c r="S16" s="3"/>
-    </row>
-    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T16" s="3"/>
+      <c r="U16" s="3"/>
+    </row>
+    <row r="17" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1193,17 +1247,23 @@
       <c r="P17" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="Q17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S17" s="3">
         <v>296300</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>235900</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>362800</v>
       </c>
     </row>
-    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1246,17 +1306,23 @@
       <c r="P18" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="Q18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S18" s="3">
         <v>31900</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>17500</v>
       </c>
-      <c r="S18" s="3">
+      <c r="U18" s="3">
         <v>30400</v>
       </c>
     </row>
-    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1276,8 +1342,10 @@
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
       <c r="S19" s="3"/>
-    </row>
-    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T19" s="3"/>
+      <c r="U19" s="3"/>
+    </row>
+    <row r="20" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1320,17 +1388,23 @@
       <c r="P20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="Q20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S20" s="3">
         <v>3100</v>
       </c>
-      <c r="R20" s="3">
+      <c r="T20" s="3">
         <v>8200</v>
       </c>
-      <c r="S20" s="3">
+      <c r="U20" s="3">
         <v>9000</v>
       </c>
     </row>
-    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1382,8 +1456,14 @@
       <c r="S21" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="U21" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="22" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1426,17 +1506,23 @@
       <c r="P22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="Q22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S22" s="3">
         <v>2000</v>
       </c>
-      <c r="R22" s="3">
+      <c r="T22" s="3">
         <v>1800</v>
       </c>
-      <c r="S22" s="3">
+      <c r="U22" s="3">
         <v>1400</v>
       </c>
     </row>
-    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -1479,17 +1565,23 @@
       <c r="P23" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="Q23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S23" s="3">
         <v>32900</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>23900</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>37900</v>
       </c>
     </row>
-    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1532,17 +1624,23 @@
       <c r="P24" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="Q24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S24" s="3">
         <v>5400</v>
       </c>
-      <c r="R24" s="3">
+      <c r="T24" s="3">
         <v>5200</v>
       </c>
-      <c r="S24" s="3">
+      <c r="U24" s="3">
         <v>7100</v>
       </c>
     </row>
-    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1594,8 +1692,14 @@
       <c r="S25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T25" s="3">
+        <v>0</v>
+      </c>
+      <c r="U25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -1638,17 +1742,23 @@
       <c r="P26" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="Q26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S26" s="3">
         <v>27500</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>18700</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>30900</v>
       </c>
     </row>
-    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -1691,17 +1801,23 @@
       <c r="P27" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="Q27" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R27" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S27" s="3">
         <v>27500</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>18700</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>30900</v>
       </c>
     </row>
-    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1753,8 +1869,14 @@
       <c r="S28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T28" s="3">
+        <v>0</v>
+      </c>
+      <c r="U28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1797,17 +1919,23 @@
       <c r="P29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q29" s="3">
-        <v>0</v>
-      </c>
-      <c r="R29" s="3">
-        <v>0</v>
+      <c r="Q29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="S29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T29" s="3">
+        <v>0</v>
+      </c>
+      <c r="U29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1859,8 +1987,14 @@
       <c r="S30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T30" s="3">
+        <v>0</v>
+      </c>
+      <c r="U30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1912,8 +2046,14 @@
       <c r="S31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T31" s="3">
+        <v>0</v>
+      </c>
+      <c r="U31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1956,17 +2096,23 @@
       <c r="P32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="Q32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S32" s="3">
         <v>-3100</v>
       </c>
-      <c r="R32" s="3">
+      <c r="T32" s="3">
         <v>-8200</v>
       </c>
-      <c r="S32" s="3">
+      <c r="U32" s="3">
         <v>-9000</v>
       </c>
     </row>
-    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -2009,17 +2155,23 @@
       <c r="P33" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="Q33" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R33" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S33" s="3">
         <v>27500</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>18700</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>30900</v>
       </c>
     </row>
-    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2071,8 +2223,14 @@
       <c r="S34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T34" s="3">
+        <v>0</v>
+      </c>
+      <c r="U34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -2115,75 +2273,87 @@
       <c r="P35" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="Q35" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R35" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S35" s="3">
         <v>27500</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>18700</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>30900</v>
       </c>
     </row>
-    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44196</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>44012</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>43830</v>
       </c>
     </row>
-    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2203,8 +2373,10 @@
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
       <c r="S39" s="3"/>
-    </row>
-    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T39" s="3"/>
+      <c r="U39" s="3"/>
+    </row>
+    <row r="40" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2224,235 +2396,261 @@
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
       <c r="S40" s="3"/>
-    </row>
-    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T40" s="3"/>
+      <c r="U40" s="3"/>
+    </row>
+    <row r="41" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>45300</v>
+      </c>
+      <c r="E41" s="3">
+        <v>45300</v>
+      </c>
+      <c r="F41" s="3">
         <v>76300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>76300</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>80900</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>81600</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>407900</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>407800</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>108100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>107800</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>244500</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>243900</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>103900</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>103700</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>395900</v>
       </c>
-      <c r="Q41" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="R41" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="S41" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="S41" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="T41" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="U41" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>432700</v>
+      </c>
+      <c r="E42" s="3">
+        <v>432800</v>
+      </c>
+      <c r="F42" s="3">
         <v>405100</v>
       </c>
-      <c r="E42" s="3">
+      <c r="G42" s="3">
         <v>405200</v>
       </c>
-      <c r="F42" s="3">
+      <c r="H42" s="3">
         <v>397300</v>
       </c>
-      <c r="G42" s="3">
+      <c r="I42" s="3">
         <v>400900</v>
       </c>
-      <c r="H42" s="3">
+      <c r="J42" s="3">
         <v>65800</v>
       </c>
-      <c r="I42" s="3">
+      <c r="K42" s="3">
         <v>65800</v>
       </c>
-      <c r="J42" s="3">
+      <c r="L42" s="3">
         <v>356800</v>
       </c>
-      <c r="K42" s="3">
+      <c r="M42" s="3">
         <v>356000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="N42" s="3">
         <v>227100</v>
       </c>
-      <c r="M42" s="3">
+      <c r="O42" s="3">
         <v>226500</v>
       </c>
-      <c r="N42" s="3">
+      <c r="P42" s="3">
         <v>370600</v>
       </c>
-      <c r="O42" s="3">
+      <c r="Q42" s="3">
         <v>369900</v>
       </c>
-      <c r="P42" s="3">
+      <c r="R42" s="3">
         <v>78600</v>
       </c>
-      <c r="Q42" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="R42" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="S42" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="S42" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="T42" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="U42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>78800</v>
+      </c>
+      <c r="E43" s="3">
+        <v>78800</v>
+      </c>
+      <c r="F43" s="3">
         <v>65900</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>65900</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>67300</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>67900</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>70400</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>70400</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>87500</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>87300</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>83200</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>83000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>78100</v>
       </c>
-      <c r="O43" s="3">
+      <c r="Q43" s="3">
         <v>78000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="R43" s="3">
         <v>75200</v>
       </c>
-      <c r="Q43" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="R43" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="S43" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="S43" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="T43" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="U43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>8400</v>
+      </c>
+      <c r="E44" s="3">
+        <v>8400</v>
+      </c>
+      <c r="F44" s="3">
         <v>7200</v>
       </c>
-      <c r="E44" s="3">
+      <c r="G44" s="3">
         <v>7200</v>
       </c>
-      <c r="F44" s="3">
+      <c r="H44" s="3">
         <v>8500</v>
       </c>
-      <c r="G44" s="3">
+      <c r="I44" s="3">
         <v>8600</v>
       </c>
-      <c r="H44" s="3">
+      <c r="J44" s="3">
         <v>21600</v>
       </c>
-      <c r="I44" s="3">
+      <c r="K44" s="3">
         <v>21600</v>
       </c>
-      <c r="J44" s="3">
+      <c r="L44" s="3">
         <v>9200</v>
       </c>
-      <c r="K44" s="3">
+      <c r="M44" s="3">
         <v>9200</v>
       </c>
-      <c r="L44" s="3">
+      <c r="N44" s="3">
         <v>13200</v>
       </c>
-      <c r="M44" s="3">
+      <c r="O44" s="3">
         <v>13200</v>
       </c>
-      <c r="N44" s="3">
+      <c r="P44" s="3">
         <v>8800</v>
       </c>
-      <c r="O44" s="3">
+      <c r="Q44" s="3">
         <v>8800</v>
       </c>
-      <c r="P44" s="3">
+      <c r="R44" s="3">
         <v>12800</v>
       </c>
-      <c r="Q44" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="R44" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="S44" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="S44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="T44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="U44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
+      <c r="D45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F45" s="3">
         <v>25600</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>25600</v>
       </c>
-      <c r="F45" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G45" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="H45" s="3" t="s">
         <v>8</v>
       </c>
@@ -2486,223 +2684,253 @@
       <c r="R45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="S45" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="S45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="T45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="U45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>620900</v>
+      </c>
+      <c r="E46" s="3">
+        <v>621000</v>
+      </c>
+      <c r="F46" s="3">
         <v>632600</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>632900</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>608500</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>614000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>615800</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>615600</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>619700</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>618300</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>620200</v>
-      </c>
-      <c r="M46" s="3">
-        <v>618700</v>
-      </c>
-      <c r="N46" s="3">
-        <v>619800</v>
       </c>
       <c r="O46" s="3">
         <v>618700</v>
       </c>
       <c r="P46" s="3">
+        <v>619800</v>
+      </c>
+      <c r="Q46" s="3">
+        <v>618700</v>
+      </c>
+      <c r="R46" s="3">
         <v>612600</v>
       </c>
-      <c r="Q46" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="R46" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="S46" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="S46" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="T46" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="U46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>12500</v>
+        <v>13400</v>
       </c>
       <c r="E47" s="3">
-        <v>12500</v>
+        <v>13400</v>
       </c>
       <c r="F47" s="3">
         <v>12500</v>
       </c>
       <c r="G47" s="3">
+        <v>12500</v>
+      </c>
+      <c r="H47" s="3">
+        <v>12500</v>
+      </c>
+      <c r="I47" s="3">
         <v>12600</v>
       </c>
-      <c r="H47" s="3">
+      <c r="J47" s="3">
         <v>14500</v>
       </c>
-      <c r="I47" s="3">
+      <c r="K47" s="3">
         <v>14500</v>
       </c>
-      <c r="J47" s="3">
+      <c r="L47" s="3">
         <v>13100</v>
       </c>
-      <c r="K47" s="3">
+      <c r="M47" s="3">
         <v>13000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="N47" s="3">
         <v>14000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="O47" s="3">
         <v>13900</v>
       </c>
-      <c r="N47" s="3">
+      <c r="P47" s="3">
         <v>17200</v>
       </c>
-      <c r="O47" s="3">
+      <c r="Q47" s="3">
         <v>17200</v>
       </c>
-      <c r="P47" s="3">
+      <c r="R47" s="3">
         <v>20100</v>
       </c>
-      <c r="Q47" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="R47" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="S47" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="S47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="T47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="U47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>389800</v>
+      </c>
+      <c r="E48" s="3">
         <v>389900</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
+        <v>389900</v>
+      </c>
+      <c r="G48" s="3">
         <v>390100</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>413600</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>417300</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>432800</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>432700</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>437200</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>436200</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>447400</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>446300</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>443800</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>443100</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>448600</v>
       </c>
-      <c r="Q48" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="R48" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="S48" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="S48" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="T48" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="U48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>621500</v>
+      </c>
+      <c r="E49" s="3">
+        <v>621700</v>
+      </c>
+      <c r="F49" s="3">
         <v>620000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>620300</v>
       </c>
-      <c r="F49" s="3">
+      <c r="H49" s="3">
         <v>638000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="I49" s="3">
         <v>643700</v>
       </c>
-      <c r="H49" s="3">
+      <c r="J49" s="3">
         <v>670100</v>
       </c>
-      <c r="I49" s="3">
+      <c r="K49" s="3">
         <v>669900</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>691800</v>
       </c>
-      <c r="K49" s="3">
+      <c r="M49" s="3">
         <v>690300</v>
       </c>
-      <c r="L49" s="3">
+      <c r="N49" s="3">
         <v>717800</v>
       </c>
-      <c r="M49" s="3">
+      <c r="O49" s="3">
         <v>716000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="P49" s="3">
         <v>741500</v>
       </c>
-      <c r="O49" s="3">
+      <c r="Q49" s="3">
         <v>740300</v>
       </c>
-      <c r="P49" s="3">
+      <c r="R49" s="3">
         <v>770400</v>
       </c>
-      <c r="Q49" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="R49" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="S49" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="S49" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="T49" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="U49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2754,8 +2982,14 @@
       <c r="S50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T50" s="3">
+        <v>0</v>
+      </c>
+      <c r="U50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2807,61 +3041,73 @@
       <c r="S51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T51" s="3">
+        <v>0</v>
+      </c>
+      <c r="U51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>68500</v>
+      </c>
+      <c r="E52" s="3">
+        <v>68500</v>
+      </c>
+      <c r="F52" s="3">
         <v>52300</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
         <v>52300</v>
       </c>
-      <c r="F52" s="3">
+      <c r="H52" s="3">
         <v>51300</v>
       </c>
-      <c r="G52" s="3">
+      <c r="I52" s="3">
         <v>51800</v>
       </c>
-      <c r="H52" s="3">
+      <c r="J52" s="3">
         <v>50300</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>50300</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>45500</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>45400</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>45300</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>45200</v>
       </c>
-      <c r="N52" s="3">
+      <c r="P52" s="3">
         <v>42200</v>
       </c>
-      <c r="O52" s="3">
+      <c r="Q52" s="3">
         <v>42200</v>
       </c>
-      <c r="P52" s="3">
+      <c r="R52" s="3">
         <v>46300</v>
       </c>
-      <c r="Q52" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="R52" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="S52" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="S52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="T52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="U52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2913,61 +3159,73 @@
       <c r="S53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T53" s="3">
+        <v>0</v>
+      </c>
+      <c r="U53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1729800</v>
+      </c>
+      <c r="E54" s="3">
+        <v>1730200</v>
+      </c>
+      <c r="F54" s="3">
         <v>1723100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>1723800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>1736800</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>1752400</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>1798500</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>1798100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>1822200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>1818100</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>1863800</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>1859300</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>1882200</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>1879000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>1918100</v>
       </c>
-      <c r="Q54" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="R54" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="S54" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="S54" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="T54" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="U54" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2987,8 +3245,10 @@
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
       <c r="S55" s="3"/>
-    </row>
-    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T55" s="3"/>
+      <c r="U55" s="3"/>
+    </row>
+    <row r="56" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3008,326 +3268,364 @@
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
       <c r="S56" s="3"/>
-    </row>
-    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T56" s="3"/>
+      <c r="U56" s="3"/>
+    </row>
+    <row r="57" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>27900</v>
+      </c>
+      <c r="E57" s="3">
+        <v>27900</v>
+      </c>
+      <c r="F57" s="3">
         <v>19100</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>19200</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>21300</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>21500</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>17600</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>17600</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>18200</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>18100</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>22300</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>22200</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>25100</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>25100</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>25300</v>
       </c>
-      <c r="Q57" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="R57" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="S57" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="S57" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="T57" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="U57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>39800</v>
+      </c>
+      <c r="E58" s="3">
+        <v>39800</v>
+      </c>
+      <c r="F58" s="3">
         <v>34600</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>34600</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>39000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="I58" s="3">
         <v>39300</v>
       </c>
-      <c r="H58" s="3">
+      <c r="J58" s="3">
         <v>42900</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>42900</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>42800</v>
       </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>42700</v>
       </c>
-      <c r="L58" s="3">
+      <c r="N58" s="3">
         <v>39900</v>
       </c>
-      <c r="M58" s="3">
+      <c r="O58" s="3">
         <v>39800</v>
       </c>
-      <c r="N58" s="3">
+      <c r="P58" s="3">
         <v>40300</v>
       </c>
-      <c r="O58" s="3">
+      <c r="Q58" s="3">
         <v>40300</v>
       </c>
-      <c r="P58" s="3">
+      <c r="R58" s="3">
         <v>39100</v>
       </c>
-      <c r="Q58" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="R58" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="S58" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="S58" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="T58" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="U58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>180800</v>
+      </c>
+      <c r="E59" s="3">
+        <v>180900</v>
+      </c>
+      <c r="F59" s="3">
         <v>177700</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>177700</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>163400</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>164900</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>173900</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>173900</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>184400</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>184000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>191100</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>190700</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>183400</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>183100</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>188700</v>
       </c>
-      <c r="Q59" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="R59" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="S59" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="S59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="T59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="U59" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>275300</v>
+      </c>
+      <c r="E60" s="3">
+        <v>275400</v>
+      </c>
+      <c r="F60" s="3">
         <v>256200</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>256300</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>247900</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>250100</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>258600</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>258600</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>269200</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>268600</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>276900</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>276200</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>271900</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>271500</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>271500</v>
       </c>
-      <c r="Q60" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="R60" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="S60" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="S60" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="T60" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="U60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>27700</v>
+      </c>
+      <c r="E61" s="3">
+        <v>27700</v>
+      </c>
+      <c r="F61" s="3">
         <v>17000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>17000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>18900</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>19000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>16700</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>16700</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>21500</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>21500</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>21800</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>21700</v>
       </c>
-      <c r="N61" s="3">
+      <c r="P61" s="3">
         <v>26800</v>
       </c>
-      <c r="O61" s="3">
+      <c r="Q61" s="3">
         <v>26800</v>
       </c>
-      <c r="P61" s="3">
+      <c r="R61" s="3">
         <v>19400</v>
       </c>
-      <c r="Q61" s="3">
-        <v>0</v>
-      </c>
-      <c r="R61" s="3">
-        <v>0</v>
-      </c>
       <c r="S61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T61" s="3">
+        <v>0</v>
+      </c>
+      <c r="U61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>268900</v>
+      </c>
+      <c r="E62" s="3">
+        <v>269000</v>
+      </c>
+      <c r="F62" s="3">
         <v>251400</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>251500</v>
       </c>
-      <c r="F62" s="3">
+      <c r="H62" s="3">
         <v>264300</v>
       </c>
-      <c r="G62" s="3">
+      <c r="I62" s="3">
         <v>266700</v>
       </c>
-      <c r="H62" s="3">
+      <c r="J62" s="3">
         <v>272200</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>272100</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>283200</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>282500</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>287600</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>286900</v>
       </c>
-      <c r="N62" s="3">
+      <c r="P62" s="3">
         <v>298400</v>
       </c>
-      <c r="O62" s="3">
+      <c r="Q62" s="3">
         <v>297800</v>
       </c>
-      <c r="P62" s="3">
+      <c r="R62" s="3">
         <v>304100</v>
       </c>
-      <c r="Q62" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="R62" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="S62" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="S62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="T62" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="U62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3379,8 +3677,14 @@
       <c r="S63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T63" s="3">
+        <v>0</v>
+      </c>
+      <c r="U63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3432,8 +3736,14 @@
       <c r="S64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T64" s="3">
+        <v>0</v>
+      </c>
+      <c r="U64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3485,61 +3795,73 @@
       <c r="S65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T65" s="3">
+        <v>0</v>
+      </c>
+      <c r="U65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>593700</v>
+      </c>
+      <c r="E66" s="3">
+        <v>593900</v>
+      </c>
+      <c r="F66" s="3">
         <v>547700</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>547900</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>553600</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>558600</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>571200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>571100</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>593300</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>592000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>601900</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>600400</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>606400</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>605400</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>601100</v>
       </c>
-      <c r="Q66" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="R66" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="S66" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="S66" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="T66" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="U66" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3559,8 +3881,10 @@
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
       <c r="S67" s="3"/>
-    </row>
-    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T67" s="3"/>
+      <c r="U67" s="3"/>
+    </row>
+    <row r="68" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3612,8 +3936,14 @@
       <c r="S68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T68" s="3">
+        <v>0</v>
+      </c>
+      <c r="U68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3665,8 +3995,14 @@
       <c r="S69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T69" s="3">
+        <v>0</v>
+      </c>
+      <c r="U69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3718,8 +4054,14 @@
       <c r="S70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T70" s="3">
+        <v>0</v>
+      </c>
+      <c r="U70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3771,61 +4113,73 @@
       <c r="S71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T71" s="3">
+        <v>0</v>
+      </c>
+      <c r="U71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-441300</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-441500</v>
+      </c>
+      <c r="F72" s="3">
         <v>-414200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>-414400</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>-392700</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>-396300</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>-365400</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>-365300</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>-351700</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>-350900</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>-317900</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>-317100</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>-298600</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>-298100</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>-265600</v>
       </c>
-      <c r="Q72" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="R72" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="S72" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="S72" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="T72" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="U72" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3877,8 +4231,14 @@
       <c r="S73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T73" s="3">
+        <v>0</v>
+      </c>
+      <c r="U73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3930,8 +4290,14 @@
       <c r="S74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T74" s="3">
+        <v>0</v>
+      </c>
+      <c r="U74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3983,61 +4349,73 @@
       <c r="S75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T75" s="3">
+        <v>0</v>
+      </c>
+      <c r="U75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1136000</v>
+      </c>
+      <c r="E76" s="3">
+        <v>1136300</v>
+      </c>
+      <c r="F76" s="3">
         <v>1175400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>1175900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>1183200</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>1193800</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>1227300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>1227000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>1228800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>1226100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>1261900</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>1258900</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>1275800</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>1273600</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>1317000</v>
       </c>
-      <c r="Q76" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="R76" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="S76" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="S76" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="T76" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="U76" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4089,66 +4467,78 @@
       <c r="S77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T77" s="3">
+        <v>0</v>
+      </c>
+      <c r="U77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:21" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44196</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>44012</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>43830</v>
       </c>
     </row>
-    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -4191,17 +4581,23 @@
       <c r="P81" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="Q81" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R81" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S81" s="3">
         <v>27500</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>18700</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>30900</v>
       </c>
     </row>
-    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4221,61 +4617,69 @@
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
       <c r="S82" s="3"/>
-    </row>
-    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T82" s="3"/>
+      <c r="U82" s="3"/>
+    </row>
+    <row r="83" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D83" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E83" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F83" s="3">
+      <c r="D83" s="3">
+        <v>47500</v>
+      </c>
+      <c r="E83" s="3">
+        <v>47900</v>
+      </c>
+      <c r="F83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H83" s="3">
         <v>47200</v>
       </c>
-      <c r="G83" s="3">
+      <c r="I83" s="3">
         <v>47100</v>
       </c>
-      <c r="H83" s="3">
+      <c r="J83" s="3">
         <v>11300</v>
       </c>
-      <c r="I83" s="3">
+      <c r="K83" s="3">
         <v>11300</v>
       </c>
-      <c r="J83" s="3">
+      <c r="L83" s="3">
         <v>47200</v>
       </c>
-      <c r="K83" s="3">
+      <c r="M83" s="3">
         <v>47100</v>
       </c>
-      <c r="L83" s="3">
+      <c r="N83" s="3">
         <v>12800</v>
       </c>
-      <c r="M83" s="3">
+      <c r="O83" s="3">
         <v>12700</v>
       </c>
-      <c r="N83" s="3">
+      <c r="P83" s="3">
         <v>45600</v>
       </c>
-      <c r="O83" s="3">
+      <c r="Q83" s="3">
         <v>45600</v>
       </c>
-      <c r="P83" s="3">
+      <c r="R83" s="3">
         <v>12600</v>
       </c>
-      <c r="Q83" s="3">
-        <v>0</v>
-      </c>
-      <c r="R83" s="3">
-        <v>0</v>
-      </c>
       <c r="S83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T83" s="3">
+        <v>0</v>
+      </c>
+      <c r="U83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4327,8 +4731,14 @@
       <c r="S84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T84" s="3">
+        <v>0</v>
+      </c>
+      <c r="U84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4380,8 +4790,14 @@
       <c r="S85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T85" s="3">
+        <v>0</v>
+      </c>
+      <c r="U85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4433,8 +4849,14 @@
       <c r="S86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T86" s="3">
+        <v>0</v>
+      </c>
+      <c r="U86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4486,8 +4908,14 @@
       <c r="S87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T87" s="3">
+        <v>0</v>
+      </c>
+      <c r="U87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4539,61 +4967,73 @@
       <c r="S88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T88" s="3">
+        <v>0</v>
+      </c>
+      <c r="U88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="D89" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E89" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F89" s="3">
+      <c r="D89" s="3">
+        <v>48300</v>
+      </c>
+      <c r="E89" s="3">
+        <v>48300</v>
+      </c>
+      <c r="F89" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G89" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H89" s="3">
         <v>42500</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>42900</v>
       </c>
-      <c r="H89" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I89" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J89" s="3">
+      <c r="J89" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K89" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L89" s="3">
         <v>33900</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>33800</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>32900</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>32800</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>39100</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>39000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>37200</v>
       </c>
-      <c r="Q89" s="3">
-        <v>0</v>
-      </c>
-      <c r="R89" s="3">
-        <v>0</v>
-      </c>
       <c r="S89" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T89" s="3">
+        <v>0</v>
+      </c>
+      <c r="U89" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4613,61 +5053,69 @@
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
       <c r="S90" s="3"/>
-    </row>
-    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T90" s="3"/>
+      <c r="U90" s="3"/>
+    </row>
+    <row r="91" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E91" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F91" s="3">
+      <c r="D91" s="3">
+        <v>-10800</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-10800</v>
+      </c>
+      <c r="F91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H91" s="3">
         <v>-11100</v>
       </c>
-      <c r="G91" s="3">
+      <c r="I91" s="3">
         <v>-11200</v>
       </c>
-      <c r="H91" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I91" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J91" s="3">
+      <c r="J91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L91" s="3">
         <v>-10600</v>
       </c>
-      <c r="K91" s="3">
+      <c r="M91" s="3">
         <v>-10600</v>
       </c>
-      <c r="L91" s="3">
+      <c r="N91" s="3">
         <v>-20400</v>
       </c>
-      <c r="M91" s="3">
+      <c r="O91" s="3">
         <v>-20300</v>
       </c>
-      <c r="N91" s="3">
+      <c r="P91" s="3">
         <v>-10400</v>
       </c>
-      <c r="O91" s="3">
+      <c r="Q91" s="3">
         <v>-10400</v>
       </c>
-      <c r="P91" s="3">
+      <c r="R91" s="3">
         <v>-21700</v>
       </c>
-      <c r="Q91" s="3">
-        <v>0</v>
-      </c>
-      <c r="R91" s="3">
-        <v>0</v>
-      </c>
       <c r="S91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T91" s="3">
+        <v>0</v>
+      </c>
+      <c r="U91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4719,8 +5167,14 @@
       <c r="S92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T92" s="3">
+        <v>0</v>
+      </c>
+      <c r="U92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4772,61 +5226,73 @@
       <c r="S93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T93" s="3">
+        <v>0</v>
+      </c>
+      <c r="U93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E94" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F94" s="3">
+      <c r="D94" s="3">
+        <v>-36100</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-36100</v>
+      </c>
+      <c r="F94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H94" s="3">
         <v>-175000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>-176500</v>
       </c>
-      <c r="H94" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I94" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J94" s="3">
+      <c r="J94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K94" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L94" s="3">
         <v>-73400</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>-73200</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>56800</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>56700</v>
       </c>
-      <c r="N94" s="3">
+      <c r="P94" s="3">
         <v>-155100</v>
       </c>
-      <c r="O94" s="3">
+      <c r="Q94" s="3">
         <v>-154800</v>
       </c>
-      <c r="P94" s="3">
+      <c r="R94" s="3">
         <v>144700</v>
       </c>
-      <c r="Q94" s="3">
-        <v>0</v>
-      </c>
-      <c r="R94" s="3">
-        <v>0</v>
-      </c>
       <c r="S94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T94" s="3">
+        <v>0</v>
+      </c>
+      <c r="U94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4846,61 +5312,69 @@
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
       <c r="S95" s="3"/>
-    </row>
-    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T95" s="3"/>
+      <c r="U95" s="3"/>
+    </row>
+    <row r="96" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E96" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F96" s="3">
+      <c r="D96" s="3">
         <v>16000</v>
       </c>
-      <c r="G96" s="3">
+      <c r="E96" s="3">
+        <v>16000</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H96" s="3">
+        <v>16000</v>
+      </c>
+      <c r="I96" s="3">
         <v>16100</v>
       </c>
-      <c r="H96" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I96" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J96" s="3">
+      <c r="J96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L96" s="3">
         <v>16100</v>
       </c>
-      <c r="K96" s="3">
+      <c r="M96" s="3">
         <v>16000</v>
       </c>
-      <c r="L96" s="3">
+      <c r="N96" s="3">
         <v>7000</v>
       </c>
-      <c r="M96" s="3">
+      <c r="O96" s="3">
         <v>7000</v>
       </c>
-      <c r="N96" s="3">
+      <c r="P96" s="3">
         <v>16000</v>
       </c>
-      <c r="O96" s="3">
+      <c r="Q96" s="3">
         <v>16000</v>
       </c>
-      <c r="P96" s="3">
+      <c r="R96" s="3">
         <v>7100</v>
       </c>
-      <c r="Q96" s="3">
-        <v>0</v>
-      </c>
-      <c r="R96" s="3">
-        <v>0</v>
-      </c>
       <c r="S96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T96" s="3">
+        <v>0</v>
+      </c>
+      <c r="U96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4952,8 +5426,14 @@
       <c r="S97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T97" s="3">
+        <v>0</v>
+      </c>
+      <c r="U97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5005,8 +5485,14 @@
       <c r="S98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T98" s="3">
+        <v>0</v>
+      </c>
+      <c r="U98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5058,61 +5544,73 @@
       <c r="S99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T99" s="3">
+        <v>0</v>
+      </c>
+      <c r="U99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E100" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F100" s="3">
+      <c r="D100" s="3">
+        <v>-28200</v>
+      </c>
+      <c r="E100" s="3">
+        <v>-28200</v>
+      </c>
+      <c r="F100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H100" s="3">
         <v>-28900</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>-29200</v>
       </c>
-      <c r="H100" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I100" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J100" s="3">
+      <c r="J100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K100" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L100" s="3">
         <v>-28800</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>-28700</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>-19600</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>-19500</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>-29000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>-29000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="R100" s="3">
         <v>-19900</v>
       </c>
-      <c r="Q100" s="3">
-        <v>0</v>
-      </c>
-      <c r="R100" s="3">
-        <v>0</v>
-      </c>
       <c r="S100" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T100" s="3">
+        <v>0</v>
+      </c>
+      <c r="U100" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -5155,66 +5653,78 @@
       <c r="P101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q101" s="3">
-        <v>0</v>
-      </c>
-      <c r="R101" s="3">
-        <v>0</v>
+      <c r="Q101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="S101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T101" s="3">
+        <v>0</v>
+      </c>
+      <c r="U101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:21" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>0</v>
+        <v>-15900</v>
       </c>
       <c r="E102" s="3">
-        <v>0</v>
+        <v>-15900</v>
       </c>
       <c r="F102" s="3">
+        <v>0</v>
+      </c>
+      <c r="G102" s="3">
+        <v>0</v>
+      </c>
+      <c r="H102" s="3">
         <v>-161300</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>-162800</v>
       </c>
-      <c r="H102" s="3">
-        <v>0</v>
-      </c>
-      <c r="I102" s="3">
-        <v>0</v>
-      </c>
       <c r="J102" s="3">
+        <v>0</v>
+      </c>
+      <c r="K102" s="3">
+        <v>0</v>
+      </c>
+      <c r="L102" s="3">
         <v>-68300</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>-68100</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>70100</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>70000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>-145000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>-144800</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>162000</v>
       </c>
-      <c r="Q102" s="3">
-        <v>0</v>
-      </c>
-      <c r="R102" s="3">
-        <v>0</v>
-      </c>
       <c r="S102" s="3">
+        <v>0</v>
+      </c>
+      <c r="T102" s="3">
+        <v>0</v>
+      </c>
+      <c r="U102" s="3">
         <v>0</v>
       </c>
     </row>
